--- a/review/abilities/workbooks/26_Class_Shadow.xlsx
+++ b/review/abilities/workbooks/26_Class_Shadow.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -211,7 +211,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -248,19 +248,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1399,15 +1386,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1729,15 +1713,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2056,15 +2037,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2736,15 +2714,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3388,15 +3363,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3420,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3435,12 +3407,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="12" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="12" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3521,30 +3492,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3568,7 +3534,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3588,7 +3553,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3608,7 +3572,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3628,7 +3591,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3648,7 +3610,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3668,7 +3629,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3688,7 +3648,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3708,7 +3667,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3728,7 +3686,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3748,7 +3705,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3768,7 +3724,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3788,23 +3743,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/review/abilities/workbooks/26_Class_Shadow.xlsx
+++ b/review/abilities/workbooks/26_Class_Shadow.xlsx
@@ -759,21 +759,21 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>• Level 1: Slip away, land quietly, or cover an ally's passage.</t>
+          <t>• Level 1: Start with a bleed, a vanish, or a lie.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Level 3: Cross difficult ground, strike and leave, or open a lock quickly.</t>
+          <t>• Level 3: Cripple a target, open the way, or read the room.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Level 7: Shroud an escape, exploit a companion's disabling effect, or hide a party's trail.</t>
+          <t>• Level 7: Interrupt an action, become a ghost, or cut with a word.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Mobility and infiltration class. Signatures move, hide, exploit conditions and open routes. The class is at its best when it can choose the angle of attack and leave before the enemy can answer.</t>
+          <t>Infiltrator and opportunist. Access, precision and social leverage; the class wins by choosing the moment.</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Excellent action-free movement; Strike and Vanish and Fade Behind make the class feel slippery; Unseen Passage is a powerful escape/assassination tool. Open the Way gives a noncombat niche.</t>
+          <t>Clear Blade, Ghost and Face split at every tier. Strong access and control without sustained damage or healing.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Unseen Passage may trivialize encounters. Open the Way and Leave No Pursuit are campaign-dependent. The class has few direct damage options, so it relies on shared attack cards and positioning.</t>
+          <t>Reaction competition at level 7. The Blade interrupt and the Face debuff both want the same scene moment. Watch the 3 Boon stealth.</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Playtest Unseen Passage first; consider ending the shroud at the end of the current turn or requiring concealment. State that Open the Way/Leave No Pursuit are specialist picks. Add one direct-damage signature if the class feels too passive.</t>
+          <t>Playtest The Half-Second interrupt and One with the Dark's 3 Boons. Clarify social tag counting.</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Fade Behind; Soft Landing; Turn Their Eye</t>
+          <t>Blade in the Back; Fade Behind; Fast Talk</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -890,7 +890,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Pass the Guard; Strike and Vanish; Open the Way</t>
+          <t>Hamstring; Open the Way; Read the Room</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Unseen Passage; Exploit Confusion; Leave No Pursuit</t>
+          <t>The Half-Second; One with the Dark; The Cutting Word</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -964,14 +964,10 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Ten signature abilities are clear power spikes: a level-1 intercept, Aid for two allies, repeatable free attacks, a round of untargetability, party-wide movement, an 8-hour watch buff, and 2-Boon reactions.</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Playtest these first. Consider once-per-round limits, adjacency requirements, shorter durations, or 1 Boon instead of 2 where the spike is largest. Keep the fantasy; tighten the repeatability.</t>
-        </is>
-      </c>
+          <t>Redesign supersedes the earlier power-spike finding; re-check after playtest.</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n"/>
     </row>
     <row r="41" ht="79" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -1040,8 +1036,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1195,71 +1191,79 @@
     <row r="5" ht="66.5" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Fade Behind</t>
+          <t>Blade in the Back</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-shadow-fade-behind</t>
+          <t>signature-shadow-soft-landing</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Self, when you use Disengage.</t>
+          <t>One creature within reach that has not noticed you or is adjacent to one of your allies.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>As part of Disengage, move up to 2 squares without provoking. This additional movement makes no audible footfalls but does not silence speech or deliberately used equipment. It does not grant Hidden in open view; actual concealment still matters.</t>
+          <t>Make an Agility roll against the target. Weak: 3 physical damage. Standard: 4 physical damage, and the target has Bleeding 1. Strong: 6 physical damage, and the target has Bleeding 2.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>As part of Disengage, move up to 2 squares without provoking. This additional movement makes no audible footfalls but does not silence speech or deliberately used equipment. It does not grant Hidden in open view; actual concealment still matters.</t>
+          <t>Make an Agility roll against the target. Weak: 3 physical damage. Standard: 4 physical damage, and the target has Bleeding 1. Strong: 6 physical damage, and the target has Bleeding 2.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Disengage grants an extra 2-square silent move; core mobility and a clean expression of the Shadow.</t>
+          <t>Blade: Agility opener above Basic Melee; Bleeding at Standard and Strong.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the extra movement is in addition to Disengage's normal movement and whether it can pass through difficult terrain.</t>
+          <t>Approved: Main Action, Agility. 3 / 4 + Bleeding 1 / 6 + Bleeding 2; target must be unaware or engaged with an ally.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="79" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Soft Landing</t>
+          <t>Fade Behind</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-shadow-soft-landing</t>
+          <t>signature-shadow-fade-behind</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1269,51 +1273,59 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self; a visible supported free landing within 2 squares.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Jump to the destination without provoking. You may cross a gap or low obstacle but not a wall or an occupied standing creature’s square. Land standing without audible footfalls. This grants no protection from a separate fall and requires a landing you can reach within the printed distance.</t>
+          <t>Disengage. Then attempt to Hide with 1 Boon, even if you are currently observed, provided you have cover or obscurement. You still make the ordinary Hide attempt. If you succeed, you are Hidden until you attack, are revealed, or the concealment ends.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Jump to the destination without provoking. You may cross a gap or low obstacle but not a wall or an occupied standing creature’s square. Land standing without audible footfalls. This grants no protection from a separate fall and requires a landing you can reach within the printed distance.</t>
+          <t>Disengage. Then attempt to Hide with 1 Boon, even if you are currently observed, provided you have cover or obscurement. You still make the ordinary Hide attempt. If you succeed, you are Hidden until you attack, are revealed, or the concealment ends.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Jump 2 squares without provoking and land standing; niche but thematic and useful in vertical spaces.</t>
+          <t>Ghost: one Maneuver to Disengage and vanish with a Boon.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it can cross a gap wider than 2 squares if the landing is within 2, and whether it negates falling damage (text says no).</t>
+          <t>Approved: Maneuver. Disengage, then attempt to Hide with 1 Boon if you have cover.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="79" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Turn Their Eye</t>
+          <t>Fast Talk</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1328,46 +1340,54 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>One willing ally within 3 squares that can perceive your signal.</t>
+          <t>One creature within 5 squares that can hear and understand you.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Provide a plausible distraction that nearby observers can see or hear. The ally may move up to 2 squares without provoking and gains 1 Boon to its next roll to remain unnoticed before the start of your next turn. The movement itself grants no Hidden in open view.</t>
+          <t>State the social goal you are pursuing and what you want the target to do. Make a Guile roll. The result adds progress toward that goal: Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. The DA sets the progress target before the roll. When the total reaches it, the target agrees within its wants and limits. This does not compel self-harm, betrayal, or a change to its loyalties.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Provide a plausible distraction that nearby observers can see or hear. The ally may move up to 2 squares without provoking and gains 1 Boon to its next roll to remain unnoticed before the start of your next turn. The movement itself grants no Hidden in open view.</t>
+          <t>State the social goal you are pursuing and what you want the target to do. Make a Guile roll. The result adds progress toward that goal: Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. The DA sets the progress target before the roll. When the total reaches it, the target agrees within its wants and limits. This does not compel self-harm, betrayal, or a change to its loyalties.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Ally moves 2 and gains a stealth Boon; good support and a reason to coordinate.</t>
+          <t>Face: social progress at 2/3/5 toward a DA-set target.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon applies to hiding or any unnoticed roll, and whether it requires concealment.</t>
+          <t>Approved: Maneuver, Guile. Add 2/3/5 progress toward a social goal; the DA sets the target.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1518,12 +1538,12 @@
     <row r="5" ht="129" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Open the Way</t>
+          <t>Hamstring</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-shadow-open-the-way</t>
+          <t>signature-shadow-strike-and-vanish</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1533,168 +1553,188 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Guile</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One adjacent ordinary lock.</t>
+          <t>One creature within reach or range.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Use lock tools to work toward the DA’s stated opening target. Each attempt takes a Main Action, in or out of combat.</t>
+          <t>Make an Agility roll against the target. Weak: 2 physical damage, and the target has Slowed 1. Standard: 3 physical damage, and the target has Slowed 1 and Dazed 1. Strong: 5 physical damage, and the target has Slowed 1, Dazed 1 and Prone.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Use lock tools to work toward the DA’s stated opening target. Each attempt takes a Main Action, in or out of combat.
-• Weak: Add 2 progress.
-• Standard: Add 3 progress.
-• Strong: Add 4 progress.
-Your tool work makes no audible noise and leaves no tool marks. This does not silence the door or disarm a linked trap; the DA states any known risk before you begin.</t>
+          <t>Make an Agility roll against the target. Weak: 2 physical damage, and the target has Slowed 1. Standard: 3 physical damage, and the target has Slowed 1 and Dazed 1. Strong: 5 physical damage, and the target has Slowed 1, Dazed 1 and Prone.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Guile-based lockpicking with 2/3/4 progress and no noise or tool marks; strong in lock-heavy campaigns.</t>
+          <t>Blade: precision strike that trades damage for Slowed, Dazed and Prone.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Narrow for a class signature slot. Consider adding a trap-disarm or door-barring clause, or move it to shared Subterfuge.</t>
+          <t>Approved: Main Action, Agility. 2 + Slowed 1 / 3 + Slowed 1 + Dazed 1 / 5 + Slowed 1 + Dazed 1 + Prone.</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="66.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pass the Guard</t>
+          <t>Open the Way</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-shadow-pass-the-guard</t>
+          <t>signature-shadow-open-the-way</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self; a legal route of up to 3 squares.</t>
+          <t>One adjacent lock, simple trap, or hidden entrance.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Move up to 3 squares without provoking. Ignore the extra cost of difficult terrain during this move, but do not cross standing occupied squares or barriers. The movement grants no attack or automatic Hidden.</t>
+          <t>Use appropriate tools to work toward the DA's stated target. Each attempt takes a Main Action. Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. On completion, open the lock, disable the trap, or find the entrance. Your work makes no audible noise and leaves no trace. The DA states any known risk before you begin.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Move up to 3 squares without provoking. Ignore the extra cost of difficult terrain during this move, but do not cross standing occupied squares or barriers. The movement grants no attack or automatic Hidden.</t>
+          <t>Use appropriate tools to work toward the DA's stated target. Each attempt takes a Main Action. Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. On completion, open the lock, disable the trap, or find the entrance. Your work makes no audible noise and leaves no trace. The DA states any known risk before you begin.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Move 3 ignoring difficult terrain; strong infiltration mobility.</t>
+          <t>Ghost: locks, simple traps and hidden ways at 2/3/5 progress, silent and traceless.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it can cross a gap or only difficult terrain (text says no gaps) and whether it can move through an occupied ally's square.</t>
+          <t>Approved: Main Action, Guile. 2/3/5 progress to open a lock, disable a simple trap, or find a hidden entrance.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="66.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Strike and Vanish</t>
+          <t>Read the Room</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-shadow-strike-and-vanish</t>
+          <t>signature-shadow-pass-the-guard</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self, after your Main Action attack resolves.</t>
+          <t>One creature within 5 squares that you can see.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>After any result, move up to 1 square without provoking. After a Standard or Strong result, move up to 3 squares instead. An attack from Hidden ends Hidden normally; this movement does not automatically hide you again.</t>
+          <t>Make a Guile roll against the target. An intent is what the creature wants from this exchange or what it means to do next. Weak: learn one intent. Standard: learn one intent, and gain 1 Boon to your next social roll against it. Strong: learn one intent, and gain 2 Boons to your next social roll against it.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>After any result, move up to 1 square without provoking. After a Standard or Strong result, move up to 3 squares instead. An attack from Hidden ends Hidden normally; this movement does not automatically hide you again.</t>
+          <t>Make a Guile roll against the target. An intent is what the creature wants from this exchange or what it means to do next. Weak: learn one intent. Standard: learn one intent, and gain 1 Boon to your next social roll against it. Strong: learn one intent, and gain 2 Boons to your next social roll against it.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Move 1 after any attack, 3 after a Standard/Strong; excellent hit-and-run.</t>
+          <t>Face: read an intent, then carry 1 or 2 Boons into the next social roll.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Strong; monitor with Unseen Passage. Clarify whether the movement can occur after a spell or only a Main Action attack.</t>
+          <t>Approved: Maneuver, Guile. Learn one intent; 1 Boon (Standard) or 2 Boons (Strong) to the next social roll.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -1845,7 +1885,7 @@
     <row r="5" ht="79" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Exploit Confusion</t>
+          <t>The Half-Second</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -1860,56 +1900,64 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>A visible enemy within 3 squares, after another creature applies temporary Dazed, Blinded or Frightened to it.</t>
+          <t>The triggering creature.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares toward that enemy without provoking. If you finish adjacent, make one free Basic Melee attack using Brawn; on Strong you may also move 1 square without provoking afterward. You need a melee weapon and must be able to attack.</t>
+          <t>Trigger: another creature you can see declares an action. Make an Agility attack roll with a weapon against the target. Weak: 3 physical damage. The triggering action resolves. Standard: 5 physical damage. The triggering action is interrupted and lost. Strong: 7 physical damage, and the target has Dazed 1. The triggering action is interrupted and lost.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares toward that enemy without provoking. If you finish adjacent, make one free Basic Melee attack using Brawn; on Strong you may also move 1 square without provoking afterward. You need a melee weapon and must be able to attack. If the triggering condition came from a free attack, it cannot trigger this card’s free attack. No further free attacks arise from your attack.</t>
+          <t>Trigger: another creature you can see declares an action. Make an Agility attack roll with a weapon against the target. Weak: 3 physical damage. The triggering action resolves. Standard: 5 physical damage. The triggering action is interrupted and lost. Strong: 7 physical damage, and the target has Dazed 1. The triggering action is interrupted and lost.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Reaction move 2 plus a free attack when an enemy gains Dazed, Blinded or Frightened; strong but conditional.</t>
+          <t>Blade: interrupt a declared action; Standard or Strong cancels it.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify that the condition must be applied by another creature (text says yes) and whether it triggers on your own condition application.</t>
+          <t>Approved: Reaction, Agility. 3 / 5 / 7 damage; Standard or Strong cancels the declared action.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Leave No Pursuit</t>
+          <t>One with the Dark</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-shadow-leave-no-pursuit</t>
+          <t>signature-shadow-unseen-passage</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1919,106 +1967,121 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Self and up to six willing companions following your route outside combat.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Spend ten minutes preparing a departure from a campsite or other stopping place. Conceal ordinary traces of the departure and guide the group for up to one hour. Attempts to follow those ordinary tracks take 2 Banes. This does not erase magical marks, remove witnesses or conceal people from direct view.</t>
+          <t>Once per scene, while you are in dim light or darkness, become Hidden until you attack, are revealed, or enter bright light. While Hidden this way, you always roll with 3 Boons to stay hidden or remain concealed. You can move normally; the DA judges whether the concealment and your route are plausible.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Spend ten minutes preparing a departure from a campsite or other stopping place. Conceal ordinary traces of the departure and guide the group for up to one hour. Attempts to follow those ordinary tracks take 2 Banes. This does not erase magical marks, remove witnesses or conceal people from direct view. The protection ends where the party leaves your guidance or creates a conspicuous new trail.</t>
+          <t>Once per scene, while you are in dim light or darkness, become Hidden until you attack, are revealed, or enter bright light. While Hidden this way, you always roll with 3 Boons to stay hidden or remain concealed. You can move normally; the DA judges whether the concealment and your route are plausible.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Ten-minute preparation to conceal the party's trail for an hour; strong exploration utility.</t>
+          <t>Ghost: scene-long Hidden in dim light or darkness with 3 Boons to stay concealed.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Campaign-dependent. Clarify whether it works in urban/underground environments and whether it affects magical tracking (no).</t>
+          <t>Approved: Main Action. Become Hidden in dim light or darkness; 3 Boons to stay concealed.</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="141.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Unseen Passage</t>
+          <t>The Cutting Word</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>signature-shadow-unseen-passage</t>
+          <t>signature-shadow-leave-no-pursuit</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Self.</t>
+          <t>One creature within 10 squares that can see or hear you.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Shroud yourself from sight, then move up to 3 squares without provoking. Until the end of your next turn, you cannot be selected as a visible target. Attacks that do not require seeing you and areas covering your square can still affect you.</t>
+          <t>Make a Guile roll against the target. The jab can be a spoken barb, a gesture, or a look. Weak: the target has Dazed 1. Standard: the target has Dazed 1 and Frightened 1. Strong: the target has Dazed 2 and Frightened 1, and it cannot take Reactions until the end of its next turn.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Shroud yourself from sight, then move up to 3 squares without provoking. Until the end of your next turn, you cannot be selected as a visible target. Attacks that do not require seeing you and areas covering your square can still affect you. You remain solid and audible; this grants no passage through barriers or occupied squares.
-The shroud ends immediately after you make an attack, cast another spell or use a card on another creature. Your own movement does not end it. This card supplies its complete concealment effect; it does not require a separate Invisible condition or change anyone else’s detection rules.</t>
+          <t>Make a Guile roll against the target. The jab can be a spoken barb, a gesture, or a look. Weak: the target has Dazed 1. Standard: the target has Dazed 1 and Frightened 1. Strong: the target has Dazed 2 and Frightened 1, and it cannot take Reactions until the end of its next turn.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Main Action shroud: cannot be selected as a visible target until the end of your next turn, plus a 3-square move. Potentially encounter-breaking.</t>
+          <t>Face: a verbal or non-verbal jab that applies Dazed, Frightened and reaction loss.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>High-power; playtest. Consider ending at the end of the current turn, requiring concealment, or keeping area attacks as the counter. Clarify how it interacts with attacks that target a square.</t>
+          <t>Approved: Maneuver, Guile. Dazed 1 / Dazed 1 + Frightened 1 / Dazed 2 + Frightened 1 + no Reactions.</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M7"/>
@@ -2167,80 +2230,84 @@
       </c>
     </row>
     <row r="5" ht="66.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A5" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>One creature within reach that has not noticed you or is adjacent to one of your allies.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Make an Agility roll against the target. Weak: 3 physical damage. Standard: 4 physical damage, and the target has Bleeding 1. Strong: 6 physical damage, and the target has Bleeding 2.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Blade: Agility opener above Basic Melee; Bleeding at Standard and Strong.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Agility. 3 / 4 + Bleeding 1 / 6 + Bleeding 2; target must be unaware or engaged with an ally.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="79" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>Fade Behind</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>signature-shadow-fade-behind</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Self, when you use Disengage.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>As part of Disengage, move up to 2 squares without provoking. This additional movement makes no audible footfalls but does not silence speech or deliberately used equipment. It does not grant Hidden in open view; actual concealment still matters.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Disengage grants an extra 2-square silent move; core mobility and a clean expression of the Shadow.</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Clarify whether the extra movement is in addition to Disengage's normal movement and whether it can pass through difficult terrain.</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="79" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Soft Landing</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>signature-shadow-soft-landing</t>
-        </is>
-      </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Maneuver</t>
@@ -2248,51 +2315,57 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Self; a visible supported free landing within 2 squares.</t>
+          <t>Self.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Jump to the destination without provoking. You may cross a gap or low obstacle but not a wall or an occupied standing creature’s square. Land standing without audible footfalls. This grants no protection from a separate fall and requires a landing you can reach within the printed distance.</t>
+          <t>Disengage. Then attempt to Hide with 1 Boon, even if you are currently observed, provided you have cover or obscurement. You still make the ordinary Hide attempt. If you succeed, you are Hidden until you attack, are revealed, or the concealment ends.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Jump 2 squares without provoking and land standing; niche but thematic and useful in vertical spaces.</t>
+          <t>Ghost: one Maneuver to Disengage and vanish with a Boon.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether it can cross a gap wider than 2 squares if the landing is within 2, and whether it negates falling damage (text says no).</t>
+          <t>Approved: Maneuver. Disengage, then attempt to Hide with 1 Boon if you have cover.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
-      <c r="M6" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="79" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Turn Their Eye</t>
+          <t>Fast Talk</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -2307,228 +2380,252 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>One willing ally within 3 squares that can perceive your signal.</t>
+          <t>One creature within 5 squares that can hear and understand you.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Provide a plausible distraction that nearby observers can see or hear. The ally may move up to 2 squares without provoking and gains 1 Boon to its next roll to remain unnoticed before the start of your next turn. The movement itself grants no Hidden in open view.</t>
+          <t>State the social goal you are pursuing and what you want the target to do. Make a Guile roll. The result adds progress toward that goal: Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. The DA sets the progress target before the roll. When the total reaches it, the target agrees within its wants and limits. This does not compel self-harm, betrayal, or a change to its loyalties.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Ally moves 2 and gains a stealth Boon; good support and a reason to coordinate.</t>
+          <t>Face: social progress at 2/3/5 toward a DA-set target.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon applies to hiding or any unnoticed roll, and whether it requires concealment.</t>
+          <t>Approved: Maneuver, Guile. Add 2/3/5 progress toward a social goal; the DA sets the target.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="41.5" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A8" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>One creature within reach or range.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Make an Agility roll against the target. Weak: 2 physical damage, and the target has Slowed 1. Standard: 3 physical damage, and the target has Slowed 1 and Dazed 1. Strong: 5 physical damage, and the target has Slowed 1, Dazed 1 and Prone.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Blade: precision strike that trades damage for Slowed, Dazed and Prone.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Agility. 2 + Slowed 1 / 3 + Slowed 1 + Dazed 1 / 5 + Slowed 1 + Dazed 1 + Prone.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66.5" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
           <t>Open the Way</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>signature-shadow-open-the-way</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Main Action</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Guile</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>One adjacent ordinary lock.</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Use lock tools to work toward the DA’s stated opening target. Each attempt takes a Main Action, in or out of combat.</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Guile-based lockpicking with 2/3/4 progress and no noise or tool marks; strong in lock-heavy campaigns.</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Narrow for a class signature slot. Consider adding a trap-disarm or door-barring clause, or move it to shared Subterfuge.</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="66.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Pass the Guard</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>One adjacent lock, simple trap, or hidden entrance.</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Use appropriate tools to work toward the DA's stated target. Each attempt takes a Main Action. Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. On completion, open the lock, disable the trap, or find the entrance. Your work makes no audible noise and leaves no trace. The DA states any known risk before you begin.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Ghost: locks, simple traps and hidden ways at 2/3/5 progress, silent and traceless.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Approved: Main Action, Guile. 2/3/5 progress to open a lock, disable a simple trap, or find a hidden entrance.</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66.5" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>signature-shadow-pass-the-guard</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Maneuver</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Self; a legal route of up to 3 squares.</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Move up to 3 squares without provoking. Ignore the extra cost of difficult terrain during this move, but do not cross standing occupied squares or barriers. The movement grants no attack or automatic Hidden.</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Move 3 ignoring difficult terrain; strong infiltration mobility.</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Clarify whether it can cross a gap or only difficult terrain (text says no gaps) and whether it can move through an occupied ally's square.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="66.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Strike and Vanish</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>signature-shadow-strike-and-vanish</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Self, after your Main Action attack resolves.</t>
+          <t>One creature within 5 squares that you can see.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>After any result, move up to 1 square without provoking. After a Standard or Strong result, move up to 3 squares instead. An attack from Hidden ends Hidden normally; this movement does not automatically hide you again.</t>
+          <t>Make a Guile roll against the target. An intent is what the creature wants from this exchange or what it means to do next. Weak: learn one intent. Standard: learn one intent, and gain 1 Boon to your next social roll against it. Strong: learn one intent, and gain 2 Boons to your next social roll against it.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Move 1 after any attack, 3 after a Standard/Strong; excellent hit-and-run.</t>
+          <t>Face: read an intent, then carry 1 or 2 Boons into the next social roll.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Strong; monitor with Unseen Passage. Clarify whether the movement can occur after a spell or only a Main Action attack.</t>
+          <t>Approved: Maneuver, Guile. Learn one intent; 1 Boon (Standard) or 2 Boons (Strong) to the next social roll.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr"/>
-      <c r="M10" s="8" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="66.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A11" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Exploit Confusion</t>
+          <t>The Half-Second</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2543,159 +2640,179 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Agility</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>A visible enemy within 3 squares, after another creature applies temporary Dazed, Blinded or Frightened to it.</t>
+          <t>The triggering creature.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Move up to 2 squares toward that enemy without provoking. If you finish adjacent, make one free Basic Melee attack using Brawn; on Strong you may also move 1 square without provoking afterward. You need a melee weapon and must be able to attack.</t>
+          <t>Trigger: another creature you can see declares an action. Make an Agility attack roll with a weapon against the target. Weak: 3 physical damage. The triggering action resolves. Standard: 5 physical damage. The triggering action is interrupted and lost. Strong: 7 physical damage, and the target has Dazed 1. The triggering action is interrupted and lost.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Reaction move 2 plus a free attack when an enemy gains Dazed, Blinded or Frightened; strong but conditional.</t>
+          <t>Blade: interrupt a declared action; Standard or Strong cancels it.</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Clarify that the condition must be applied by another creature (text says yes) and whether it triggers on your own condition application.</t>
+          <t>Approved: Reaction, Agility. 3 / 5 / 7 damage; Standard or Strong cancels the declared action.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="91.5" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A12" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Leave No Pursuit</t>
+          <t>One with the Dark</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>None (no roll)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Once per scene, while you are in dim light or darkness, become Hidden until you attack, are revealed, or enter bright light. While Hidden this way, you always roll with 3 Boons to stay hidden or remain concealed. You can move normally; the DA judges whether the concealment and your route are plausible.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Ghost: scene-long Hidden in dim light or darkness with 3 Boons to stay concealed.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Approved: Main Action. Become Hidden in dim light or darkness; 3 Boons to stay concealed.</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66.5" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
           <t>signature-shadow-leave-no-pursuit</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Main Action</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>None — no roll</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Self and up to six willing companions following your route outside combat.</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Spend ten minutes preparing a departure from a campsite or other stopping place. Conceal ordinary traces of the departure and guide the group for up to one hour. Attempts to follow those ordinary tracks take 2 Banes. This does not erase magical marks, remove witnesses or conceal people from direct view.</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Ten-minute preparation to conceal the party's trail for an hour; strong exploration utility.</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>Campaign-dependent. Clarify whether it works in urban/underground environments and whether it affects magical tracking (no).</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr"/>
-      <c r="M12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="66.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Unseen Passage</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>signature-shadow-unseen-passage</t>
-        </is>
-      </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Main Action</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Self.</t>
+          <t>One creature within 10 squares that can see or hear you.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Shroud yourself from sight, then move up to 3 squares without provoking. Until the end of your next turn, you cannot be selected as a visible target. Attacks that do not require seeing you and areas covering your square can still affect you.</t>
+          <t>Make a Guile roll against the target. The jab can be a spoken barb, a gesture, or a look. Weak: the target has Dazed 1. Standard: the target has Dazed 1 and Frightened 1. Strong: the target has Dazed 2 and Frightened 1, and it cannot take Reactions until the end of its next turn.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Main Action shroud: cannot be selected as a visible target until the end of your next turn, plus a 3-square move. Potentially encounter-breaking.</t>
+          <t>Face: a verbal or non-verbal jab that applies Dazed, Frightened and reaction loss.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>High-power; playtest. Consider ending at the end of the current turn, requiring concealment, or keeping area attacks as the counter. Clarify how it interacts with attacks that target a square.</t>
+          <t>Approved: Maneuver, Guile. Dazed 1 / Dazed 1 + Frightened 1 / Dazed 2 + Frightened 1 + no Reactions.</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Revise</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>Approved by Bruce 2026-10-27.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M13"/>
@@ -2833,7 +2950,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>2</v>
@@ -2842,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
@@ -2866,7 +2983,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>1</v>
@@ -2875,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>0</v>
@@ -2902,13 +3019,13 @@
         <v>0</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
@@ -2986,16 +3103,16 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -3004,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
@@ -3017,16 +3134,16 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>0</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0</v>
@@ -3035,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
@@ -3054,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -3066,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -3082,14 +3199,14 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>• Unseen Passage may trivialize encounters. Open the Way and Leave No Pursuit are campaign-dependent. The class has few direct damage options, so it relies on shared attack cards and positioning.</t>
+          <t>All three level 7 signatures want a scarce moment: the Blade interrupt, the Ghost escape, and the Face debuff. Watch decision paralysis.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>• Playtest Unseen Passage first; consider ending the shroud at the end of the current turn or requiring concealment. State that Open the Way/Leave No Pursuit are specialist picks. Add one direct-damage signature if the class feels too passive.</t>
+          <t>The Blade and Face both trade damage for control. Check that Shadow does not out-control the dedicated control classes.</t>
         </is>
       </c>
     </row>
@@ -3229,121 +3346,41 @@
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Unseen Passage</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>signature-shadow-unseen-passage</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Power spike</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Untargetable by sight until end of next turn plus 3-square move.</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Playtest; consider end of current turn or a concealment requirement.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
+          <t>No row-level flags for this class. Use the design questions below.</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="29" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Open the Way</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>signature-shadow-open-the-way</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Lockpicking at Adept; campaign-dependent.</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Add a trap/door clause or move to shared Subterfuge.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="29" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Leave No Pursuit</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>signature-shadow-leave-no-pursuit</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Niche signature</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Trail concealment at Master; campaign-dependent.</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Accept as a specialist pick or add an ambush benefit.</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="inlineStr"/>
     </row>
   </sheetData>
@@ -3392,7 +3429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3517,232 +3554,5110 @@
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-001</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>You give ground without a sound, using the enemy’s reaching weapon to hide the direction of your first step.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>You give ground without a sound, and the enemy’s own reaching weapon hides the direction of your first step.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M5" s="7" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="7" t="inlineStr"/>
-      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
-      <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="8" t="inlineStr"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-002</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="7" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-003</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr"/>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-004</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Self, when you use Disengage.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Self.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M8" s="8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O8" s="8" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
-      <c r="Q8" s="8" t="inlineStr"/>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-005</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>As part of Disengage, move up to 2 squares without provoking. This additional movement makes no audible footfalls but does not silence speech or deliberately used equipment. It does not grant Hidden in open view; actual concealment still matters.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Disengage. Then attempt to Hide with 1 Boon, even if you are currently observed, provided you have cover or obscurement. You still make the ordinary Hide attempt. If you succeed, you are Hidden until you attack, are revealed, or the concealment ends.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ghost design.</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="8" t="inlineStr"/>
-      <c r="B10" s="8" t="inlineStr"/>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="8" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="8" t="inlineStr"/>
-      <c r="K10" s="8" t="inlineStr"/>
-      <c r="L10" s="8" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-006</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Immediate movement; Disengage lasts for this turn.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Immediate; Hidden uses its normal duration.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M10" s="8" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O10" s="8" t="inlineStr"/>
-      <c r="P10" s="8" t="inlineStr"/>
-      <c r="Q10" s="8" t="inlineStr"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-007</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-fade-behind</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Fade Behind</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-fade-behind.md</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Skill / Movement / Utility</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr"/>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-008</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Turn Their Eye</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>New title names the Face effect.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M12" s="8" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O12" s="8" t="inlineStr"/>
-      <c r="P12" s="8" t="inlineStr"/>
-      <c r="Q12" s="8" t="inlineStr"/>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-009</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>You send a glance and a tiny distracting motion toward one side while your companion slips quietly toward the other.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>You are already three sentences into the lie before the guard decides to be suspicious.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-010</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Guile</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M14" s="8" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O14" s="8" t="inlineStr"/>
-      <c r="P14" s="8" t="inlineStr"/>
-      <c r="Q14" s="8" t="inlineStr"/>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" s="7" t="inlineStr"/>
-      <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>CHG-SHA-011</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>One willing ally within 3 squares that can perceive your signal.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>One creature within 5 squares that can hear and understand you.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
-      <c r="C16" s="8" t="inlineStr"/>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr"/>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>CHG-SHA-012</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Provide a plausible distraction that nearby observers can see or hear. The ally may move up to 2 squares without provoking and gains 1 Boon to its next roll to remain unnoticed before the start of your next turn. The movement itself grants no Hidden in open view.</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>State the social goal you are pursuing and what you want the target to do. Make a Guile roll. The result adds progress toward that goal: Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. The DA sets the progress target before the roll. When the total reaches it, the target agrees within its wants and limits. This does not compel self-harm, betrayal, or a change to its loyalties.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Face design.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
       <c r="M16" s="8" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
       <c r="O16" s="8" t="inlineStr"/>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr"/>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHG-SHA-013</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Movement is immediate; Boon expires when used or the start of your next turn.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Immediate progress; the negotiation persists.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CHG-SHA-014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>signature-shadow-turn-their-eye</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fast Talk</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-turn-their-eye.md</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Skill / Social / Utility</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHG-SHA-015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Soft Landing</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>New title names the Blade effect.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CHG-SHA-016</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>You vault the low rail and land on bent knees, catching your balance before a loose stone can rattle.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>You wait for the half-second when the guard turns, and the knife goes in under the ribs.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHG-SHA-017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHG-SHA-018</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CHG-SHA-019</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Self; a visible supported free landing within 2 squares.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>One creature within reach that has not noticed you or is adjacent to one of your allies.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CHG-SHA-020</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Jump to the destination without provoking. You may cross a gap or low obstacle but not a wall or an occupied standing creature’s square. Land standing without audible footfalls. This grants no protection from a separate fall and requires a landing you can reach within the printed distance.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Make an Agility roll against the target. Weak: 3 physical damage. Standard: 4 physical damage, and the target has Bleeding 1. Strong: 6 physical damage, and the target has Bleeding 2.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Blade design.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHG-SHA-021</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Immediate jump.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Immediate; Bleeding uses its normal decay.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CHG-SHA-022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>signature-shadow-soft-landing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Blade in the Back</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-soft-landing.md</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CHG-SHA-023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Strike and Vanish</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>New title names the Blade effect.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CHG-SHA-024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Your strike lands and you slip away on its follow-through, already looking for the next patch of cover.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>You cut the tendon, not the throat. The fight is already decided.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CHG-SHA-025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CHG-SHA-026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CHG-SHA-027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Self, after your Main Action attack resolves.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>One creature within reach or range.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHG-SHA-028</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>After any result, move up to 1 square without provoking. After a Standard or Strong result, move up to 3 squares instead. An attack from Hidden ends Hidden normally; this movement does not automatically hide you again.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Make an Agility roll against the target. Weak: 2 physical damage, and the target has Slowed 1. Standard: 3 physical damage, and the target has Slowed 1 and Dazed 1. Strong: 5 physical damage, and the target has Slowed 1, Dazed 1 and Prone.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Blade design.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CHG-SHA-029</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Immediate movement.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Immediate; conditions use their normal decay.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CHG-SHA-030</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CHG-SHA-031</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>signature-shadow-strike-and-vanish</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hamstring</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-strike-and-vanish.md</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Once on your turn; no benefit from free attacks.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CHG-SHA-032</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>signature-shadow-open-the-way</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open the Way</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-open-the-way.md</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>You find the lock’s rhythm through the tool, work its stubborn point and ease it open without a click.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>There is always another door. You just have to know where the hinges are.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CHG-SHA-033</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>signature-shadow-open-the-way</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open the Way</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-open-the-way.md</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>One adjacent ordinary lock.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>One adjacent lock, simple trap, or hidden entrance.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHG-SHA-034</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>signature-shadow-open-the-way</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open the Way</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-open-the-way.md</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Use lock tools to work toward the DA’s stated opening target. Each attempt takes a Main Action, in or out of combat. - **Weak:** Add 2 progress. - **Standard:** Add 3 progress. - **Strong:** Add 4 progress. Your tool work makes no audible noise and leaves no tool marks. This does not silence the door or disarm a linked trap; the DA states any known risk before you begin.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Use appropriate tools to work toward the DA's stated target. Each attempt takes a Main Action. Weak: 2 progress. Standard: 3 progress. Strong: 5 progress. On completion, open the lock, disable the trap, or find the entrance. Your work makes no audible noise and leaves no trace. The DA states any known risk before you begin.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ghost design.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHG-SHA-035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>signature-shadow-open-the-way</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open the Way</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-open-the-way.md</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Progress persists for that lock.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Progress persists for that task.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHG-SHA-036</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pass the Guard</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>New title names the Face effect.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CHG-SHA-037</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>You slip along the blind side of the struggle, ducking below a reach and stepping through the open space beyond.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>You find the one thing the other side wants and set it on the table.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CHG-SHA-038</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Guile</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CHG-SHA-039</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Self; a legal route of up to 3 squares.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>One creature within 5 squares that you can see.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CHG-SHA-040</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Move up to 3 squares without provoking. Ignore the extra cost of difficult terrain during this move, but do not cross standing occupied squares or barriers. The movement grants no attack or automatic Hidden.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Make a Guile roll against the target. An intent is what the creature wants from this exchange or what it means to do next. Weak: learn one intent. Standard: learn one intent, and gain 1 Boon to your next social roll against it. Strong: learn one intent, and gain 2 Boons to your next social roll against it.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Face design.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CHG-SHA-041</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Immediate movement.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>The scene.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CHG-SHA-042</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Skill / Movement</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Skill / Social / Utility</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHG-SHA-043</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>signature-shadow-pass-the-guard</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Read the Room</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-pass-the-guard.md</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Once per scene per creature.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHG-SHA-044</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Exploit Confusion</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>New title names the Blade effect.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CHG-SHA-045</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>You see the enemy stagger under a companion’s blow and dart in before they can gather themselves.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>You move in the space between a decision and its consequence.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHG-SHA-046</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Agility</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHG-SHA-047</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>A visible enemy within 3 squares, after another creature applies temporary Dazed, Blinded or Frightened to it.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>The triggering creature.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CHG-SHA-048</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Move up to 2 squares toward that enemy without provoking. If you finish adjacent, make one free Basic Melee attack using Brawn; on Strong you may also move 1 square without provoking afterward. You need a melee weapon and must be able to attack. If the triggering condition came from a free attack, it cannot trigger this card’s free attack. No further free attacks arise from your attack.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Trigger: another creature you can see declares an action. Make an Agility attack roll with a weapon against the target. Weak: 3 physical damage. The triggering action resolves. Standard: 5 physical damage. The triggering action is interrupted and lost. Strong: 7 physical damage, and the target has Dazed 1. The triggering action is interrupted and lost.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Blade design.</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CHG-SHA-049</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Immediate approach, attack and possible exit.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Immediate.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CHG-SHA-050</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Movement</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Skill / Attack / Control</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CHG-SHA-051</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>signature-shadow-exploit-confusion</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>The Half-Second</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-exploit-confusion.md</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Once per scene; uses your Reaction.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CHG-SHA-052</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Unseen Passage</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>New title names the Ghost effect.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHG-SHA-053</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>You draw the surrounding shadow across your body like a cloak and slip away while your outline fades from sight.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>They search the room three times. You are standing in the corner.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CHG-SHA-054</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Shroud yourself from sight, then move up to 3 squares without provoking. Until the end of your next turn, you cannot be selected as a visible target. Attacks that do not require seeing you and areas covering your square can still affect you. You remain solid and audible; this grants no passage through barriers or occupied squares. The shroud ends immediately after you make an attack, cast another spell or use a card on another creature. Your own movement does not end it. This card supplies its complete concealment effect; it does not require a separate Invisible condition or change anyone else’s detection rules.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Once per scene, while you are in dim light or darkness, become Hidden until you attack, are revealed, or enter bright light. While Hidden this way, you always roll with 3 Boons to stay hidden or remain concealed. You can move normally; the DA judges whether the concealment and your route are plausible.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Ghost design.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CHG-SHA-055</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Until the end of your next turn, or immediately after an ending action.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Until you attack, are revealed, or enter bright light.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHG-SHA-056</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Magic / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Skill / Utility / Movement</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CHG-SHA-057</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>signature-shadow-unseen-passage</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>One with the Dark</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-unseen-passage.md</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Repeatable; normal action economy applies.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CHG-SHA-058</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Leave No Pursuit</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>New title names the Face effect.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CHG-SHA-059</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Narrative</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>You brush away the obvious prints, point out the stones that keep none and lead the party off the route their pursuers expect.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>You find the sentence that undoes them, and say it quietly.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Narrative matches the redesigned effect.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CHG-SHA-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Main Action</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Maneuver</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Action changed for the new timing.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CHG-SHA-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>None — no roll</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Guile</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Attribute set for the new roll.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CHG-SHA-062</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Target / range</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Self and up to six willing companions following your route outside combat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>One creature within 10 squares that can see or hear you.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Targeting redefined for the new effect.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CHG-SHA-063</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Spend ten minutes preparing a departure from a campsite or other stopping place. Conceal ordinary traces of the departure and guide the group for up to one hour. Attempts to follow those ordinary tracks take 2 Banes. This does not erase magical marks, remove witnesses or conceal people from direct view. The protection ends where the party leaves your guidance or creates a conspicuous new trail.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Make a Guile roll against the target. The jab can be a spoken barb, a gesture, or a look. Weak: the target has Dazed 1. Standard: the target has Dazed 1 and Frightened 1. Strong: the target has Dazed 2 and Frightened 1, and it cannot take Reactions until the end of its next turn.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Rewritten to the approved Face design.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CHG-SHA-064</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>The concealed trail remains difficult to follow until new evidence exposes it.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Conditions use their normal decay.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Duration set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CHG-SHA-065</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Skill / Utility</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Skill / Social / Control</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Tags updated for the new effect.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CHG-SHA-066</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CLS-07</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>signature-shadow-leave-no-pursuit</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>The Cutting Word</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>design/cards/signature-shadow-leave-no-pursuit.md</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>One application per departure; repeated preparation does not add more Banes.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Once per scene.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Limit set for the new effect.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>bruceamoser/heroes-of-legend-foundry#252</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Stable ID retained.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q204"/>
